--- a/sources/table_normalization/xlsx/education-table19.xlsx
+++ b/sources/table_normalization/xlsx/education-table19.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="CA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -187,8 +187,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="#,##0_)"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0_)"/>
+    <numFmt numFmtId="164" formatCode="#,##0_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0_)"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -827,7 +827,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -860,144 +860,144 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="35" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1005,43 +1005,121 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="3" fillId="2" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="3" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="3" fillId="2" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="3" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="3" fillId="2" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="3" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="36" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="3" fillId="2" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="2" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="37" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="16" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="13" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="13" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="2" borderId="34" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="16" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="12" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="13" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="34" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="37" fontId="7" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="37" fontId="7" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1058,122 +1136,32 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="7" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="7" fillId="4" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="9" fillId="5" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="9" fillId="5" borderId="33" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="9" fillId="5" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1556,34 +1544,34 @@
       <c r="Z1" s="13"/>
     </row>
     <row r="2" spans="1:26" s="2" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="113"/>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
+      <c r="B2" s="122"/>
+      <c r="C2" s="122"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="122"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="122"/>
+      <c r="P2" s="122"/>
+      <c r="Q2" s="122"/>
+      <c r="R2" s="122"/>
+      <c r="S2" s="122"/>
+      <c r="T2" s="122"/>
+      <c r="U2" s="122"/>
+      <c r="V2" s="122"/>
+      <c r="W2" s="122"/>
+      <c r="X2" s="122"/>
+      <c r="Y2" s="122"/>
+      <c r="Z2" s="122"/>
     </row>
     <row r="3" spans="1:26" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="14"/>
@@ -1614,167 +1602,167 @@
       <c r="Z3" s="16"/>
     </row>
     <row r="4" spans="1:26" s="3" customFormat="1" ht="25" customHeight="1">
-      <c r="A4" s="117" t="s">
+      <c r="A4" s="128" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="118" t="s">
+      <c r="B4" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="129" t="s">
+      <c r="D4" s="117"/>
+      <c r="E4" s="134" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="130"/>
-      <c r="Q4" s="130"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="108" t="s">
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="135"/>
+      <c r="O4" s="135"/>
+      <c r="P4" s="135"/>
+      <c r="Q4" s="135"/>
+      <c r="R4" s="136"/>
+      <c r="S4" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="T4" s="109"/>
-      <c r="U4" s="108" t="s">
+      <c r="T4" s="117"/>
+      <c r="U4" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="V4" s="109"/>
-      <c r="W4" s="108" t="s">
+      <c r="V4" s="117"/>
+      <c r="W4" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="X4" s="109"/>
-      <c r="Y4" s="135" t="s">
+      <c r="X4" s="117"/>
+      <c r="Y4" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="Z4" s="136" t="s">
+      <c r="Z4" s="131" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:26" s="3" customFormat="1" ht="25" customHeight="1">
-      <c r="A5" s="121"/>
-      <c r="B5" s="122"/>
-      <c r="C5" s="123"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="97" t="s">
+      <c r="A5" s="129"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="98"/>
-      <c r="G5" s="99" t="s">
+      <c r="F5" s="124"/>
+      <c r="G5" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="98"/>
-      <c r="I5" s="100" t="s">
+      <c r="H5" s="124"/>
+      <c r="I5" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="98"/>
-      <c r="K5" s="100" t="s">
+      <c r="J5" s="124"/>
+      <c r="K5" s="126" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="98"/>
-      <c r="M5" s="100" t="s">
+      <c r="L5" s="124"/>
+      <c r="M5" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="98"/>
-      <c r="O5" s="100" t="s">
+      <c r="N5" s="124"/>
+      <c r="O5" s="126" t="s">
         <v>15</v>
       </c>
-      <c r="P5" s="98"/>
-      <c r="Q5" s="100" t="s">
+      <c r="P5" s="124"/>
+      <c r="Q5" s="126" t="s">
         <v>16</v>
       </c>
-      <c r="R5" s="101"/>
-      <c r="S5" s="110"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="110"/>
-      <c r="V5" s="111"/>
-      <c r="W5" s="110"/>
-      <c r="X5" s="111"/>
-      <c r="Y5" s="137"/>
-      <c r="Z5" s="138"/>
+      <c r="R5" s="127"/>
+      <c r="S5" s="118"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="118"/>
+      <c r="V5" s="119"/>
+      <c r="W5" s="118"/>
+      <c r="X5" s="119"/>
+      <c r="Y5" s="114"/>
+      <c r="Z5" s="132"/>
     </row>
     <row r="6" spans="1:26" s="3" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="125"/>
-      <c r="B6" s="126"/>
-      <c r="C6" s="127" t="s">
+      <c r="A6" s="130"/>
+      <c r="B6" s="112"/>
+      <c r="C6" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="128" t="s">
+      <c r="D6" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="132" t="s">
+      <c r="E6" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="133" t="s">
+      <c r="F6" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="127" t="s">
+      <c r="G6" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="133" t="s">
+      <c r="H6" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="127" t="s">
+      <c r="I6" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="133" t="s">
+      <c r="J6" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="127" t="s">
+      <c r="K6" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="133" t="s">
+      <c r="L6" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="M6" s="127" t="s">
+      <c r="M6" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="133" t="s">
+      <c r="N6" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="O6" s="127" t="s">
+      <c r="O6" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="P6" s="133" t="s">
+      <c r="P6" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="Q6" s="127" t="s">
+      <c r="Q6" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="R6" s="134" t="s">
+      <c r="R6" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="S6" s="132" t="s">
+      <c r="S6" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="T6" s="128" t="s">
+      <c r="T6" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="U6" s="132" t="s">
+      <c r="U6" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="V6" s="128" t="s">
+      <c r="V6" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="W6" s="127" t="s">
+      <c r="W6" s="100" t="s">
         <v>17</v>
       </c>
-      <c r="X6" s="128" t="s">
+      <c r="X6" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="Y6" s="139"/>
-      <c r="Z6" s="140"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="133"/>
     </row>
     <row r="7" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A7" s="102" t="s">
+      <c r="A7" s="120" t="s">
         <v>20</v>
       </c>
       <c r="B7" s="17" t="s">
@@ -1854,7 +1842,7 @@
       </c>
     </row>
     <row r="8" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="103"/>
+      <c r="A8" s="105"/>
       <c r="B8" s="20" t="s">
         <v>22</v>
       </c>
@@ -1932,7 +1920,7 @@
       </c>
     </row>
     <row r="9" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A9" s="104"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="23" t="s">
         <v>23</v>
       </c>
@@ -2010,7 +1998,7 @@
       </c>
     </row>
     <row r="10" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A10" s="105" t="s">
+      <c r="A10" s="107" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="26" t="s">
@@ -2090,7 +2078,7 @@
       </c>
     </row>
     <row r="11" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A11" s="105"/>
+      <c r="A11" s="107"/>
       <c r="B11" s="29" t="s">
         <v>22</v>
       </c>
@@ -2168,7 +2156,7 @@
       </c>
     </row>
     <row r="12" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A12" s="106"/>
+      <c r="A12" s="108"/>
       <c r="B12" s="32" t="s">
         <v>23</v>
       </c>
@@ -2246,7 +2234,7 @@
       </c>
     </row>
     <row r="13" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A13" s="103" t="s">
+      <c r="A13" s="105" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="35" t="s">
@@ -2326,7 +2314,7 @@
       </c>
     </row>
     <row r="14" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A14" s="103"/>
+      <c r="A14" s="105"/>
       <c r="B14" s="20" t="s">
         <v>22</v>
       </c>
@@ -2404,7 +2392,7 @@
       </c>
     </row>
     <row r="15" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A15" s="104"/>
+      <c r="A15" s="106"/>
       <c r="B15" s="23" t="s">
         <v>23</v>
       </c>
@@ -2482,7 +2470,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A16" s="105" t="s">
+      <c r="A16" s="107" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="26" t="s">
@@ -2562,7 +2550,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A17" s="105"/>
+      <c r="A17" s="107"/>
       <c r="B17" s="29" t="s">
         <v>22</v>
       </c>
@@ -2640,7 +2628,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A18" s="106"/>
+      <c r="A18" s="108"/>
       <c r="B18" s="32" t="s">
         <v>23</v>
       </c>
@@ -2718,7 +2706,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A19" s="103" t="s">
+      <c r="A19" s="105" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="35" t="s">
@@ -2798,7 +2786,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A20" s="103"/>
+      <c r="A20" s="105"/>
       <c r="B20" s="20" t="s">
         <v>22</v>
       </c>
@@ -2876,7 +2864,7 @@
       </c>
     </row>
     <row r="21" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A21" s="104"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="23" t="s">
         <v>23</v>
       </c>
@@ -2954,7 +2942,7 @@
       </c>
     </row>
     <row r="22" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A22" s="105" t="s">
+      <c r="A22" s="107" t="s">
         <v>29</v>
       </c>
       <c r="B22" s="26" t="s">
@@ -3034,7 +3022,7 @@
       </c>
     </row>
     <row r="23" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A23" s="105"/>
+      <c r="A23" s="107"/>
       <c r="B23" s="29" t="s">
         <v>22</v>
       </c>
@@ -3112,7 +3100,7 @@
       </c>
     </row>
     <row r="24" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A24" s="106"/>
+      <c r="A24" s="108"/>
       <c r="B24" s="32" t="s">
         <v>23</v>
       </c>
@@ -3190,7 +3178,7 @@
       </c>
     </row>
     <row r="25" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A25" s="103" t="s">
+      <c r="A25" s="105" t="s">
         <v>30</v>
       </c>
       <c r="B25" s="35" t="s">
@@ -3270,7 +3258,7 @@
       </c>
     </row>
     <row r="26" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A26" s="103"/>
+      <c r="A26" s="105"/>
       <c r="B26" s="20" t="s">
         <v>22</v>
       </c>
@@ -3348,7 +3336,7 @@
       </c>
     </row>
     <row r="27" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A27" s="104"/>
+      <c r="A27" s="106"/>
       <c r="B27" s="23" t="s">
         <v>23</v>
       </c>
@@ -3426,7 +3414,7 @@
       </c>
     </row>
     <row r="28" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A28" s="105" t="s">
+      <c r="A28" s="107" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="26" t="s">
@@ -3506,7 +3494,7 @@
       </c>
     </row>
     <row r="29" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A29" s="105"/>
+      <c r="A29" s="107"/>
       <c r="B29" s="29" t="s">
         <v>22</v>
       </c>
@@ -3584,7 +3572,7 @@
       </c>
     </row>
     <row r="30" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A30" s="106"/>
+      <c r="A30" s="108"/>
       <c r="B30" s="32" t="s">
         <v>23</v>
       </c>
@@ -3662,7 +3650,7 @@
       </c>
     </row>
     <row r="31" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A31" s="103" t="s">
+      <c r="A31" s="105" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="35" t="s">
@@ -3742,7 +3730,7 @@
       </c>
     </row>
     <row r="32" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A32" s="103"/>
+      <c r="A32" s="105"/>
       <c r="B32" s="20" t="s">
         <v>22</v>
       </c>
@@ -3820,7 +3808,7 @@
       </c>
     </row>
     <row r="33" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A33" s="104"/>
+      <c r="A33" s="106"/>
       <c r="B33" s="23" t="s">
         <v>23</v>
       </c>
@@ -3898,7 +3886,7 @@
       </c>
     </row>
     <row r="34" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A34" s="105" t="s">
+      <c r="A34" s="107" t="s">
         <v>33</v>
       </c>
       <c r="B34" s="26" t="s">
@@ -3978,7 +3966,7 @@
       </c>
     </row>
     <row r="35" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A35" s="105"/>
+      <c r="A35" s="107"/>
       <c r="B35" s="29" t="s">
         <v>22</v>
       </c>
@@ -4056,7 +4044,7 @@
       </c>
     </row>
     <row r="36" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A36" s="106"/>
+      <c r="A36" s="108"/>
       <c r="B36" s="32" t="s">
         <v>23</v>
       </c>
@@ -4134,7 +4122,7 @@
       </c>
     </row>
     <row r="37" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A37" s="103" t="s">
+      <c r="A37" s="105" t="s">
         <v>34</v>
       </c>
       <c r="B37" s="35" t="s">
@@ -4214,7 +4202,7 @@
       </c>
     </row>
     <row r="38" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A38" s="103"/>
+      <c r="A38" s="105"/>
       <c r="B38" s="20" t="s">
         <v>22</v>
       </c>
@@ -4292,7 +4280,7 @@
       </c>
     </row>
     <row r="39" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A39" s="104"/>
+      <c r="A39" s="106"/>
       <c r="B39" s="23" t="s">
         <v>23</v>
       </c>
@@ -4370,7 +4358,7 @@
       </c>
     </row>
     <row r="40" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A40" s="105" t="s">
+      <c r="A40" s="107" t="s">
         <v>35</v>
       </c>
       <c r="B40" s="26" t="s">
@@ -4450,7 +4438,7 @@
       </c>
     </row>
     <row r="41" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A41" s="105"/>
+      <c r="A41" s="107"/>
       <c r="B41" s="29" t="s">
         <v>22</v>
       </c>
@@ -4528,7 +4516,7 @@
       </c>
     </row>
     <row r="42" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A42" s="106"/>
+      <c r="A42" s="108"/>
       <c r="B42" s="32" t="s">
         <v>23</v>
       </c>
@@ -4606,7 +4594,7 @@
       </c>
     </row>
     <row r="43" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A43" s="103" t="s">
+      <c r="A43" s="105" t="s">
         <v>36</v>
       </c>
       <c r="B43" s="35" t="s">
@@ -4686,7 +4674,7 @@
       </c>
     </row>
     <row r="44" spans="1:26" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A44" s="103"/>
+      <c r="A44" s="105"/>
       <c r="B44" s="20" t="s">
         <v>22</v>
       </c>
@@ -4764,7 +4752,7 @@
       </c>
     </row>
     <row r="45" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A45" s="107"/>
+      <c r="A45" s="109"/>
       <c r="B45" s="37" t="s">
         <v>23</v>
       </c>
@@ -4870,7 +4858,7 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47" spans="1:26" s="7" customFormat="1" ht="15" customHeight="1">
-      <c r="A47" s="114" t="str">
+      <c r="A47" s="97" t="str">
         <f>CONCATENATE("NOTE: Table reads:  Of all ",IF(ISTEXT(C9),LEFT(C9,3),TEXT(C9,"#,##0"))," public school students retained in kindergarten, ",IF(ISTEXT(E9),LEFT(E9,3),TEXT(E9,"#,##0"))," (",TEXT(F9,"0.0"),"%) were American Indian or Alaska Native, ",IF(ISTEXT(S9),LEFT(S9,3),TEXT(S9,"#,##0"))," (",TEXT(T9,"0.0"),"%) were students with disabilities served under the Individuals with Disabilities Education Act (IDEA), and ",IF(ISTEXT(U9),LEFT(U9,3),TEXT(U9,"#,##0"))," (",TEXT(V9,"0.0"),"%) were students with disabilities served solely under Section 504 of the Rehabilitation Act of 1973.")</f>
         <v>NOTE: Table reads:  Of all 12,778 public school students retained in kindergarten, 153 (1.2%) were American Indian or Alaska Native, 1,404 (11.0%) were students with disabilities served under the Individuals with Disabilities Education Act (IDEA), and 109 (0.9%) were students with disabilities served solely under Section 504 of the Rehabilitation Act of 1973.</v>
       </c>
@@ -4901,7 +4889,7 @@
       <c r="Z47" s="40"/>
     </row>
     <row r="48" spans="1:26" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A48" s="115" t="s">
+      <c r="A48" s="98" t="s">
         <v>37</v>
       </c>
       <c r="B48" s="41"/>
@@ -4929,7 +4917,7 @@
       <c r="X48" s="42"/>
     </row>
     <row r="49" spans="1:26" s="7" customFormat="1" ht="14" customHeight="1">
-      <c r="A49" s="116" t="s">
+      <c r="A49" s="99" t="s">
         <v>38</v>
       </c>
       <c r="B49" s="5"/>
@@ -4960,6 +4948,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A2:Z2"/>
+    <mergeCell ref="E4:R4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="Z4:Z6"/>
     <mergeCell ref="A37:A39"/>
     <mergeCell ref="A40:A42"/>
     <mergeCell ref="A43:A45"/>
@@ -4976,20 +4978,6 @@
     <mergeCell ref="A34:A36"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A2:Z2"/>
-    <mergeCell ref="E4:R4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="Z4:Z6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
